--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819444</v>
+        <v>119819468</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618376</v>
+        <v>618354</v>
       </c>
       <c r="R17" t="n">
-        <v>7265700</v>
+        <v>7266194</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819468</v>
+        <v>119819444</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,30 +2453,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618354</v>
+        <v>618376</v>
       </c>
       <c r="R18" t="n">
-        <v>7266194</v>
+        <v>7265700</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819460</v>
+        <v>119819449</v>
       </c>
       <c r="B9" t="n">
-        <v>89212</v>
+        <v>91884</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,30 +1454,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618478</v>
+        <v>618608</v>
       </c>
       <c r="R9" t="n">
-        <v>7266264</v>
+        <v>7265761</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819453</v>
+        <v>119819455</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618499</v>
+        <v>618552</v>
       </c>
       <c r="R10" t="n">
-        <v>7266141</v>
+        <v>7266102</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819439</v>
+        <v>119819441</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,25 +1676,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618264</v>
+        <v>618302</v>
       </c>
       <c r="R11" t="n">
-        <v>7265719</v>
+        <v>7265772</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819452</v>
+        <v>119819443</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,25 +1787,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618670</v>
+        <v>618376</v>
       </c>
       <c r="R12" t="n">
-        <v>7265829</v>
+        <v>7265703</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819466</v>
+        <v>119819435</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>91826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>3100</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618486</v>
+        <v>618300</v>
       </c>
       <c r="R14" t="n">
-        <v>7266232</v>
+        <v>7265774</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819459</v>
+        <v>119819464</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,30 +2120,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618572</v>
+        <v>618485</v>
       </c>
       <c r="R15" t="n">
-        <v>7266176</v>
+        <v>7266243</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819443</v>
+        <v>119819452</v>
       </c>
       <c r="B16" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618376</v>
+        <v>618670</v>
       </c>
       <c r="R16" t="n">
-        <v>7265703</v>
+        <v>7265829</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819468</v>
+        <v>119819442</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618354</v>
+        <v>618304</v>
       </c>
       <c r="R17" t="n">
-        <v>7266194</v>
+        <v>7265777</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819444</v>
+        <v>119819463</v>
       </c>
       <c r="B18" t="n">
         <v>91832</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618376</v>
+        <v>618487</v>
       </c>
       <c r="R18" t="n">
-        <v>7265700</v>
+        <v>7266259</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819450</v>
+        <v>119819438</v>
       </c>
       <c r="B19" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2568,21 +2568,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618632</v>
+        <v>618317</v>
       </c>
       <c r="R19" t="n">
-        <v>7265743</v>
+        <v>7265937</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819458</v>
+        <v>119819456</v>
       </c>
       <c r="B20" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618571</v>
+        <v>618574</v>
       </c>
       <c r="R20" t="n">
-        <v>7266173</v>
+        <v>7266106</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819449</v>
+        <v>119819467</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618608</v>
+        <v>618344</v>
       </c>
       <c r="R21" t="n">
-        <v>7265761</v>
+        <v>7266305</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819456</v>
+        <v>119819453</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618574</v>
+        <v>618499</v>
       </c>
       <c r="R23" t="n">
-        <v>7266106</v>
+        <v>7266141</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819465</v>
+        <v>119819461</v>
       </c>
       <c r="B24" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,25 +3119,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618489</v>
+        <v>618495</v>
       </c>
       <c r="R24" t="n">
-        <v>7266234</v>
+        <v>7266270</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819438</v>
+        <v>119819457</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,30 +3230,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618317</v>
+        <v>618642</v>
       </c>
       <c r="R25" t="n">
-        <v>7265937</v>
+        <v>7266121</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819435</v>
+        <v>119819450</v>
       </c>
       <c r="B26" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618300</v>
+        <v>618632</v>
       </c>
       <c r="R26" t="n">
-        <v>7265774</v>
+        <v>7265743</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819436</v>
+        <v>119819451</v>
       </c>
       <c r="B27" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618304</v>
+        <v>618639</v>
       </c>
       <c r="R27" t="n">
-        <v>7265775</v>
+        <v>7265727</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819446</v>
+        <v>119819466</v>
       </c>
       <c r="B28" t="n">
-        <v>91852</v>
+        <v>92030</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618407</v>
+        <v>618486</v>
       </c>
       <c r="R28" t="n">
-        <v>7265700</v>
+        <v>7266232</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819442</v>
+        <v>119819437</v>
       </c>
       <c r="B29" t="n">
         <v>91834</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618304</v>
+        <v>618321</v>
       </c>
       <c r="R29" t="n">
-        <v>7265777</v>
+        <v>7265970</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819467</v>
+        <v>119819458</v>
       </c>
       <c r="B30" t="n">
-        <v>90562</v>
+        <v>91832</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3789,21 +3789,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618344</v>
+        <v>618571</v>
       </c>
       <c r="R30" t="n">
-        <v>7266305</v>
+        <v>7266173</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819464</v>
+        <v>119819460</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>89212</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618485</v>
+        <v>618478</v>
       </c>
       <c r="R31" t="n">
-        <v>7266243</v>
+        <v>7266264</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819437</v>
+        <v>119819436</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>90807</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4007,25 +4007,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618321</v>
+        <v>618304</v>
       </c>
       <c r="R32" t="n">
-        <v>7265970</v>
+        <v>7265775</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819457</v>
+        <v>119819454</v>
       </c>
       <c r="B33" t="n">
         <v>91840</v>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618642</v>
+        <v>618497</v>
       </c>
       <c r="R33" t="n">
-        <v>7266121</v>
+        <v>7266152</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819455</v>
+        <v>119819448</v>
       </c>
       <c r="B34" t="n">
-        <v>91832</v>
+        <v>91856</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618552</v>
+        <v>618486</v>
       </c>
       <c r="R34" t="n">
-        <v>7266102</v>
+        <v>7265809</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819441</v>
+        <v>119819446</v>
       </c>
       <c r="B35" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4340,25 +4340,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618302</v>
+        <v>618407</v>
       </c>
       <c r="R35" t="n">
-        <v>7265772</v>
+        <v>7265700</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819451</v>
+        <v>119819444</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4451,25 +4451,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618639</v>
+        <v>618376</v>
       </c>
       <c r="R36" t="n">
-        <v>7265727</v>
+        <v>7265700</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819454</v>
+        <v>119819465</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4562,30 +4562,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618497</v>
+        <v>618489</v>
       </c>
       <c r="R37" t="n">
-        <v>7266152</v>
+        <v>7266234</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819448</v>
+        <v>119819439</v>
       </c>
       <c r="B38" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,25 +4673,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618486</v>
+        <v>618264</v>
       </c>
       <c r="R38" t="n">
-        <v>7265809</v>
+        <v>7265719</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819461</v>
+        <v>119819468</v>
       </c>
       <c r="B39" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4784,30 +4784,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618495</v>
+        <v>618354</v>
       </c>
       <c r="R39" t="n">
-        <v>7266270</v>
+        <v>7266194</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819463</v>
+        <v>119819459</v>
       </c>
       <c r="B40" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4899,26 +4899,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618487</v>
+        <v>618572</v>
       </c>
       <c r="R40" t="n">
-        <v>7266259</v>
+        <v>7266176</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819449</v>
+        <v>119819455</v>
       </c>
       <c r="B9" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618608</v>
+        <v>618552</v>
       </c>
       <c r="R9" t="n">
-        <v>7265761</v>
+        <v>7266102</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819455</v>
+        <v>119819441</v>
       </c>
       <c r="B10" t="n">
         <v>91832</v>
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618552</v>
+        <v>618302</v>
       </c>
       <c r="R10" t="n">
-        <v>7266102</v>
+        <v>7265772</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819441</v>
+        <v>119819449</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1680,21 +1680,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618302</v>
+        <v>618608</v>
       </c>
       <c r="R11" t="n">
-        <v>7265772</v>
+        <v>7265761</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819447</v>
+        <v>119819461</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618412</v>
+        <v>618495</v>
       </c>
       <c r="R22" t="n">
-        <v>7265705</v>
+        <v>7266270</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819461</v>
+        <v>119819447</v>
       </c>
       <c r="B24" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,30 +3119,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618495</v>
+        <v>618412</v>
       </c>
       <c r="R24" t="n">
-        <v>7266270</v>
+        <v>7265705</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819451</v>
+        <v>119819466</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>92030</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618639</v>
+        <v>618486</v>
       </c>
       <c r="R27" t="n">
-        <v>7265727</v>
+        <v>7266232</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819466</v>
+        <v>119819451</v>
       </c>
       <c r="B28" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618486</v>
+        <v>618639</v>
       </c>
       <c r="R28" t="n">
-        <v>7266232</v>
+        <v>7265727</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819460</v>
+        <v>119819436</v>
       </c>
       <c r="B31" t="n">
-        <v>89212</v>
+        <v>90807</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3900,26 +3900,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1593</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618478</v>
+        <v>618304</v>
       </c>
       <c r="R31" t="n">
-        <v>7266264</v>
+        <v>7265775</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819436</v>
+        <v>119819460</v>
       </c>
       <c r="B32" t="n">
-        <v>90807</v>
+        <v>89212</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4011,26 +4011,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>65</v>
+        <v>1593</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618304</v>
+        <v>618478</v>
       </c>
       <c r="R32" t="n">
-        <v>7265775</v>
+        <v>7266264</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819455</v>
+        <v>119819440</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91844</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,13 +1486,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618552</v>
+        <v>618304</v>
       </c>
       <c r="R9" t="n">
-        <v>7266102</v>
+        <v>7265777</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819441</v>
+        <v>119819444</v>
       </c>
       <c r="B10" t="n">
         <v>91832</v>
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618302</v>
+        <v>618376</v>
       </c>
       <c r="R10" t="n">
-        <v>7265772</v>
+        <v>7265700</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819449</v>
+        <v>119819439</v>
       </c>
       <c r="B11" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,25 +1676,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618608</v>
+        <v>618264</v>
       </c>
       <c r="R11" t="n">
-        <v>7265761</v>
+        <v>7265719</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819443</v>
+        <v>119819460</v>
       </c>
       <c r="B12" t="n">
-        <v>91884</v>
+        <v>89212</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618376</v>
+        <v>618478</v>
       </c>
       <c r="R12" t="n">
-        <v>7265703</v>
+        <v>7266264</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819440</v>
+        <v>119819449</v>
       </c>
       <c r="B13" t="n">
-        <v>91844</v>
+        <v>91884</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1898,25 +1898,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618304</v>
+        <v>618608</v>
       </c>
       <c r="R13" t="n">
-        <v>7265777</v>
+        <v>7265761</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819435</v>
+        <v>119819448</v>
       </c>
       <c r="B14" t="n">
-        <v>91826</v>
+        <v>91856</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618300</v>
+        <v>618486</v>
       </c>
       <c r="R14" t="n">
-        <v>7265774</v>
+        <v>7265809</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819464</v>
+        <v>119819456</v>
       </c>
       <c r="B15" t="n">
         <v>91840</v>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618485</v>
+        <v>618574</v>
       </c>
       <c r="R15" t="n">
-        <v>7266243</v>
+        <v>7266106</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819452</v>
+        <v>119819442</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,25 +2231,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618670</v>
+        <v>618304</v>
       </c>
       <c r="R16" t="n">
-        <v>7265829</v>
+        <v>7265777</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819442</v>
+        <v>119819466</v>
       </c>
       <c r="B17" t="n">
-        <v>91834</v>
+        <v>92030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618304</v>
+        <v>618486</v>
       </c>
       <c r="R17" t="n">
-        <v>7265777</v>
+        <v>7266232</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819463</v>
+        <v>119819452</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,30 +2453,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618487</v>
+        <v>618670</v>
       </c>
       <c r="R18" t="n">
-        <v>7266259</v>
+        <v>7265829</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819438</v>
+        <v>119819436</v>
       </c>
       <c r="B19" t="n">
-        <v>91884</v>
+        <v>90807</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5449</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618317</v>
+        <v>618304</v>
       </c>
       <c r="R19" t="n">
-        <v>7265937</v>
+        <v>7265775</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819456</v>
+        <v>119819443</v>
       </c>
       <c r="B20" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618574</v>
+        <v>618376</v>
       </c>
       <c r="R20" t="n">
-        <v>7266106</v>
+        <v>7265703</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819467</v>
+        <v>119819454</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,30 +2786,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618344</v>
+        <v>618497</v>
       </c>
       <c r="R21" t="n">
-        <v>7266305</v>
+        <v>7266152</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819461</v>
+        <v>119819447</v>
       </c>
       <c r="B22" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618495</v>
+        <v>618412</v>
       </c>
       <c r="R22" t="n">
-        <v>7266270</v>
+        <v>7265705</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819453</v>
+        <v>119819461</v>
       </c>
       <c r="B23" t="n">
-        <v>91834</v>
+        <v>91844</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,25 +3008,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618499</v>
+        <v>618495</v>
       </c>
       <c r="R23" t="n">
-        <v>7266141</v>
+        <v>7266270</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819447</v>
+        <v>119819468</v>
       </c>
       <c r="B24" t="n">
         <v>91840</v>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618412</v>
+        <v>618354</v>
       </c>
       <c r="R24" t="n">
-        <v>7265705</v>
+        <v>7266194</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819457</v>
+        <v>119819438</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,30 +3230,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618642</v>
+        <v>618317</v>
       </c>
       <c r="R25" t="n">
-        <v>7266121</v>
+        <v>7265937</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819450</v>
+        <v>119819458</v>
       </c>
       <c r="B26" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618632</v>
+        <v>618571</v>
       </c>
       <c r="R26" t="n">
-        <v>7265743</v>
+        <v>7266173</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819466</v>
+        <v>119819465</v>
       </c>
       <c r="B27" t="n">
-        <v>92030</v>
+        <v>91834</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2079</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618486</v>
+        <v>618489</v>
       </c>
       <c r="R27" t="n">
-        <v>7266232</v>
+        <v>7266234</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819451</v>
+        <v>119819464</v>
       </c>
       <c r="B28" t="n">
         <v>91840</v>
@@ -3586,7 +3586,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618639</v>
+        <v>618485</v>
       </c>
       <c r="R28" t="n">
-        <v>7265727</v>
+        <v>7266243</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819437</v>
+        <v>119819453</v>
       </c>
       <c r="B29" t="n">
         <v>91834</v>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618321</v>
+        <v>618499</v>
       </c>
       <c r="R29" t="n">
-        <v>7265970</v>
+        <v>7266141</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819458</v>
+        <v>119819463</v>
       </c>
       <c r="B30" t="n">
         <v>91832</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618571</v>
+        <v>618487</v>
       </c>
       <c r="R30" t="n">
-        <v>7266173</v>
+        <v>7266259</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819436</v>
+        <v>119819446</v>
       </c>
       <c r="B31" t="n">
-        <v>90807</v>
+        <v>91852</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,25 +3896,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>65</v>
+        <v>4366</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618304</v>
+        <v>618407</v>
       </c>
       <c r="R31" t="n">
-        <v>7265775</v>
+        <v>7265700</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819460</v>
+        <v>119819451</v>
       </c>
       <c r="B32" t="n">
-        <v>89212</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4007,30 +4007,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1593</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618478</v>
+        <v>618639</v>
       </c>
       <c r="R32" t="n">
-        <v>7266264</v>
+        <v>7265727</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819454</v>
+        <v>119819467</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>90562</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4118,30 +4118,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618497</v>
+        <v>618344</v>
       </c>
       <c r="R33" t="n">
-        <v>7266152</v>
+        <v>7266305</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819448</v>
+        <v>119819450</v>
       </c>
       <c r="B34" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618486</v>
+        <v>618632</v>
       </c>
       <c r="R34" t="n">
-        <v>7265809</v>
+        <v>7265743</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819446</v>
+        <v>119819437</v>
       </c>
       <c r="B35" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4340,25 +4340,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618407</v>
+        <v>618321</v>
       </c>
       <c r="R35" t="n">
-        <v>7265700</v>
+        <v>7265970</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,7 +4439,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819444</v>
+        <v>119819441</v>
       </c>
       <c r="B36" t="n">
         <v>91832</v>
@@ -4483,13 +4483,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618376</v>
+        <v>618302</v>
       </c>
       <c r="R36" t="n">
-        <v>7265700</v>
+        <v>7265772</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819465</v>
+        <v>119819435</v>
       </c>
       <c r="B37" t="n">
-        <v>91834</v>
+        <v>91826</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618489</v>
+        <v>618300</v>
       </c>
       <c r="R37" t="n">
-        <v>7266234</v>
+        <v>7265774</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819439</v>
+        <v>119819455</v>
       </c>
       <c r="B38" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,25 +4673,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618264</v>
+        <v>618552</v>
       </c>
       <c r="R38" t="n">
-        <v>7265719</v>
+        <v>7266102</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819468</v>
+        <v>119819459</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4784,30 +4784,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618354</v>
+        <v>618572</v>
       </c>
       <c r="R39" t="n">
-        <v>7266194</v>
+        <v>7266176</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819459</v>
+        <v>119819457</v>
       </c>
       <c r="B40" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4895,30 +4895,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618572</v>
+        <v>618642</v>
       </c>
       <c r="R40" t="n">
-        <v>7266176</v>
+        <v>7266121</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819441</v>
+        <v>119819435</v>
       </c>
       <c r="B36" t="n">
-        <v>91832</v>
+        <v>91826</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,21 +4455,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4483,13 +4483,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618302</v>
+        <v>618300</v>
       </c>
       <c r="R36" t="n">
-        <v>7265772</v>
+        <v>7265774</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819435</v>
+        <v>119819441</v>
       </c>
       <c r="B37" t="n">
-        <v>91826</v>
+        <v>91832</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618300</v>
+        <v>618302</v>
       </c>
       <c r="R37" t="n">
-        <v>7265774</v>
+        <v>7265772</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819440</v>
+        <v>119819435</v>
       </c>
       <c r="B9" t="n">
-        <v>91844</v>
+        <v>91826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4365</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618304</v>
+        <v>618300</v>
       </c>
       <c r="R9" t="n">
-        <v>7265777</v>
+        <v>7265774</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,7 +1553,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819444</v>
+        <v>119819463</v>
       </c>
       <c r="B10" t="n">
         <v>91832</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618376</v>
+        <v>618487</v>
       </c>
       <c r="R10" t="n">
-        <v>7265700</v>
+        <v>7266259</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819439</v>
+        <v>119819457</v>
       </c>
       <c r="B11" t="n">
         <v>91840</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618264</v>
+        <v>618642</v>
       </c>
       <c r="R11" t="n">
-        <v>7265719</v>
+        <v>7266121</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819460</v>
+        <v>119819453</v>
       </c>
       <c r="B12" t="n">
-        <v>89212</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618478</v>
+        <v>618499</v>
       </c>
       <c r="R12" t="n">
-        <v>7266264</v>
+        <v>7266141</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819449</v>
+        <v>119819467</v>
       </c>
       <c r="B13" t="n">
-        <v>91884</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618608</v>
+        <v>618344</v>
       </c>
       <c r="R13" t="n">
-        <v>7265761</v>
+        <v>7266305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819448</v>
+        <v>119819466</v>
       </c>
       <c r="B14" t="n">
-        <v>91856</v>
+        <v>92030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2059</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2044,7 +2044,7 @@
         <v>618486</v>
       </c>
       <c r="R14" t="n">
-        <v>7265809</v>
+        <v>7266232</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819456</v>
+        <v>119819461</v>
       </c>
       <c r="B15" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,30 +2120,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2152,13 +2152,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618574</v>
+        <v>618495</v>
       </c>
       <c r="R15" t="n">
-        <v>7266106</v>
+        <v>7266270</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819442</v>
+        <v>119819456</v>
       </c>
       <c r="B16" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618304</v>
+        <v>618574</v>
       </c>
       <c r="R16" t="n">
-        <v>7265777</v>
+        <v>7266106</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819466</v>
+        <v>119819439</v>
       </c>
       <c r="B17" t="n">
-        <v>92030</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,25 +2342,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2374,10 +2374,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618486</v>
+        <v>618264</v>
       </c>
       <c r="R17" t="n">
-        <v>7266232</v>
+        <v>7265719</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819452</v>
+        <v>119819450</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,25 +2453,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618670</v>
+        <v>618632</v>
       </c>
       <c r="R18" t="n">
-        <v>7265829</v>
+        <v>7265743</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819436</v>
+        <v>119819468</v>
       </c>
       <c r="B19" t="n">
-        <v>90807</v>
+        <v>91840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,30 +2564,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618304</v>
+        <v>618354</v>
       </c>
       <c r="R19" t="n">
-        <v>7265775</v>
+        <v>7266194</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819443</v>
+        <v>119819446</v>
       </c>
       <c r="B20" t="n">
-        <v>91884</v>
+        <v>91852</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618376</v>
+        <v>618407</v>
       </c>
       <c r="R20" t="n">
-        <v>7265703</v>
+        <v>7265700</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819454</v>
+        <v>119819438</v>
       </c>
       <c r="B21" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,30 +2786,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618497</v>
+        <v>618317</v>
       </c>
       <c r="R21" t="n">
-        <v>7266152</v>
+        <v>7265937</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819447</v>
+        <v>119819455</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618412</v>
+        <v>618552</v>
       </c>
       <c r="R22" t="n">
-        <v>7265705</v>
+        <v>7266102</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819461</v>
+        <v>119819447</v>
       </c>
       <c r="B23" t="n">
-        <v>91844</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618495</v>
+        <v>618412</v>
       </c>
       <c r="R23" t="n">
-        <v>7266270</v>
+        <v>7265705</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819468</v>
+        <v>119819443</v>
       </c>
       <c r="B24" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,30 +3119,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618354</v>
+        <v>618376</v>
       </c>
       <c r="R24" t="n">
-        <v>7266194</v>
+        <v>7265703</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819438</v>
+        <v>119819458</v>
       </c>
       <c r="B25" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618317</v>
+        <v>618571</v>
       </c>
       <c r="R25" t="n">
-        <v>7265937</v>
+        <v>7266173</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819458</v>
+        <v>119819464</v>
       </c>
       <c r="B26" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3341,30 +3341,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618571</v>
+        <v>618485</v>
       </c>
       <c r="R26" t="n">
-        <v>7266173</v>
+        <v>7266243</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819465</v>
+        <v>119819441</v>
       </c>
       <c r="B27" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618489</v>
+        <v>618302</v>
       </c>
       <c r="R27" t="n">
-        <v>7266234</v>
+        <v>7265772</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819464</v>
+        <v>119819436</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>90807</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,30 +3563,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618485</v>
+        <v>618304</v>
       </c>
       <c r="R28" t="n">
-        <v>7266243</v>
+        <v>7265775</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819453</v>
+        <v>119819448</v>
       </c>
       <c r="B29" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,21 +3678,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618499</v>
+        <v>618486</v>
       </c>
       <c r="R29" t="n">
-        <v>7266141</v>
+        <v>7265809</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819463</v>
+        <v>119819465</v>
       </c>
       <c r="B30" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3789,26 +3789,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618487</v>
+        <v>618489</v>
       </c>
       <c r="R30" t="n">
-        <v>7266259</v>
+        <v>7266234</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819446</v>
+        <v>119819460</v>
       </c>
       <c r="B31" t="n">
-        <v>91852</v>
+        <v>89212</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4366</v>
+        <v>1593</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618407</v>
+        <v>618478</v>
       </c>
       <c r="R31" t="n">
-        <v>7265700</v>
+        <v>7266264</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819451</v>
+        <v>119819437</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4007,25 +4007,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618639</v>
+        <v>618321</v>
       </c>
       <c r="R32" t="n">
-        <v>7265727</v>
+        <v>7265970</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819467</v>
+        <v>119819459</v>
       </c>
       <c r="B33" t="n">
-        <v>90562</v>
+        <v>91834</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4122,26 +4122,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618344</v>
+        <v>618572</v>
       </c>
       <c r="R33" t="n">
-        <v>7266305</v>
+        <v>7266176</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819450</v>
+        <v>119819451</v>
       </c>
       <c r="B34" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4229,25 +4229,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4261,10 +4261,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618632</v>
+        <v>618639</v>
       </c>
       <c r="R34" t="n">
-        <v>7265743</v>
+        <v>7265727</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819437</v>
+        <v>119819452</v>
       </c>
       <c r="B35" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4340,25 +4340,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618321</v>
+        <v>618670</v>
       </c>
       <c r="R35" t="n">
-        <v>7265970</v>
+        <v>7265829</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819435</v>
+        <v>119819449</v>
       </c>
       <c r="B36" t="n">
-        <v>91826</v>
+        <v>91884</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,21 +4455,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618300</v>
+        <v>618608</v>
       </c>
       <c r="R36" t="n">
-        <v>7265774</v>
+        <v>7265761</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4550,7 +4550,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819441</v>
+        <v>119819444</v>
       </c>
       <c r="B37" t="n">
         <v>91832</v>
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618302</v>
+        <v>618376</v>
       </c>
       <c r="R37" t="n">
-        <v>7265772</v>
+        <v>7265700</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819455</v>
+        <v>119819442</v>
       </c>
       <c r="B38" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,13 +4705,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618552</v>
+        <v>618304</v>
       </c>
       <c r="R38" t="n">
-        <v>7266102</v>
+        <v>7265777</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819459</v>
+        <v>119819454</v>
       </c>
       <c r="B39" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4784,30 +4784,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618572</v>
+        <v>618497</v>
       </c>
       <c r="R39" t="n">
-        <v>7266176</v>
+        <v>7266152</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819457</v>
+        <v>119819440</v>
       </c>
       <c r="B40" t="n">
-        <v>91840</v>
+        <v>91844</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4895,30 +4895,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618642</v>
+        <v>618304</v>
       </c>
       <c r="R40" t="n">
-        <v>7266121</v>
+        <v>7265777</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819441</v>
+        <v>119819436</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>90807</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618302</v>
+        <v>618304</v>
       </c>
       <c r="R27" t="n">
-        <v>7265772</v>
+        <v>7265775</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819436</v>
+        <v>119819441</v>
       </c>
       <c r="B28" t="n">
-        <v>90807</v>
+        <v>91832</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618304</v>
+        <v>618302</v>
       </c>
       <c r="R28" t="n">
-        <v>7265775</v>
+        <v>7265772</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819455</v>
+        <v>119819447</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618552</v>
+        <v>618412</v>
       </c>
       <c r="R22" t="n">
-        <v>7266102</v>
+        <v>7265705</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819447</v>
+        <v>119819455</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618412</v>
+        <v>618552</v>
       </c>
       <c r="R23" t="n">
-        <v>7265705</v>
+        <v>7266102</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819436</v>
+        <v>119819441</v>
       </c>
       <c r="B27" t="n">
-        <v>90807</v>
+        <v>91832</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>65</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618304</v>
+        <v>618302</v>
       </c>
       <c r="R27" t="n">
-        <v>7265775</v>
+        <v>7265772</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819441</v>
+        <v>119819436</v>
       </c>
       <c r="B28" t="n">
-        <v>91832</v>
+        <v>90807</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>65</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,13 +3595,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618302</v>
+        <v>618304</v>
       </c>
       <c r="R28" t="n">
-        <v>7265772</v>
+        <v>7265775</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819447</v>
+        <v>119819455</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618412</v>
+        <v>618552</v>
       </c>
       <c r="R22" t="n">
-        <v>7265705</v>
+        <v>7266102</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819455</v>
+        <v>119819447</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618552</v>
+        <v>618412</v>
       </c>
       <c r="R23" t="n">
-        <v>7266102</v>
+        <v>7265705</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819463</v>
+        <v>119819467</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>90562</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,26 +1569,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618487</v>
+        <v>618344</v>
       </c>
       <c r="R10" t="n">
-        <v>7266259</v>
+        <v>7266305</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819457</v>
+        <v>119819463</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,30 +1676,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618642</v>
+        <v>618487</v>
       </c>
       <c r="R11" t="n">
-        <v>7266121</v>
+        <v>7266259</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819453</v>
+        <v>119819457</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618499</v>
+        <v>618642</v>
       </c>
       <c r="R12" t="n">
-        <v>7266141</v>
+        <v>7266121</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819467</v>
+        <v>119819453</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>91834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618344</v>
+        <v>618499</v>
       </c>
       <c r="R13" t="n">
-        <v>7266305</v>
+        <v>7266141</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819465</v>
+        <v>119819460</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>89212</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3785,30 +3785,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618489</v>
+        <v>618478</v>
       </c>
       <c r="R30" t="n">
-        <v>7266234</v>
+        <v>7266264</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819460</v>
+        <v>119819465</v>
       </c>
       <c r="B31" t="n">
-        <v>89212</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618478</v>
+        <v>618489</v>
       </c>
       <c r="R31" t="n">
-        <v>7266264</v>
+        <v>7266234</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819455</v>
+        <v>119819447</v>
       </c>
       <c r="B22" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,13 +2929,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618552</v>
+        <v>618412</v>
       </c>
       <c r="R22" t="n">
-        <v>7266102</v>
+        <v>7265705</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819447</v>
+        <v>119819455</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618412</v>
+        <v>618552</v>
       </c>
       <c r="R23" t="n">
-        <v>7265705</v>
+        <v>7266102</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819460</v>
+        <v>119819465</v>
       </c>
       <c r="B30" t="n">
-        <v>89212</v>
+        <v>91834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3785,30 +3785,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618478</v>
+        <v>618489</v>
       </c>
       <c r="R30" t="n">
-        <v>7266264</v>
+        <v>7266234</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819465</v>
+        <v>119819460</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>89212</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618489</v>
+        <v>618478</v>
       </c>
       <c r="R31" t="n">
-        <v>7266234</v>
+        <v>7266264</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819467</v>
+        <v>119819463</v>
       </c>
       <c r="B10" t="n">
-        <v>90562</v>
+        <v>91832</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,26 +1569,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618344</v>
+        <v>618487</v>
       </c>
       <c r="R10" t="n">
-        <v>7266305</v>
+        <v>7266259</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819463</v>
+        <v>119819457</v>
       </c>
       <c r="B11" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,30 +1676,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618487</v>
+        <v>618642</v>
       </c>
       <c r="R11" t="n">
-        <v>7266259</v>
+        <v>7266121</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819457</v>
+        <v>119819453</v>
       </c>
       <c r="B12" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618642</v>
+        <v>618499</v>
       </c>
       <c r="R12" t="n">
-        <v>7266121</v>
+        <v>7266141</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819453</v>
+        <v>119819467</v>
       </c>
       <c r="B13" t="n">
-        <v>91834</v>
+        <v>90562</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618499</v>
+        <v>618344</v>
       </c>
       <c r="R13" t="n">
-        <v>7266141</v>
+        <v>7266305</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819465</v>
+        <v>119819460</v>
       </c>
       <c r="B30" t="n">
-        <v>91834</v>
+        <v>89212</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3785,30 +3785,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>1593</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618489</v>
+        <v>618478</v>
       </c>
       <c r="R30" t="n">
-        <v>7266234</v>
+        <v>7266264</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819460</v>
+        <v>119819465</v>
       </c>
       <c r="B31" t="n">
-        <v>89212</v>
+        <v>91834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,13 +3928,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618478</v>
+        <v>618489</v>
       </c>
       <c r="R31" t="n">
-        <v>7266264</v>
+        <v>7266234</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819435</v>
+        <v>119819452</v>
       </c>
       <c r="B9" t="n">
-        <v>91826</v>
+        <v>91858</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618300</v>
+        <v>618670</v>
       </c>
       <c r="R9" t="n">
-        <v>7265774</v>
+        <v>7265829</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1556,7 +1556,7 @@
         <v>119819463</v>
       </c>
       <c r="B10" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819457</v>
+        <v>119819455</v>
       </c>
       <c r="B11" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,30 +1676,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618642</v>
+        <v>618552</v>
       </c>
       <c r="R11" t="n">
-        <v>7266121</v>
+        <v>7266102</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819453</v>
+        <v>119819454</v>
       </c>
       <c r="B12" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618499</v>
+        <v>618497</v>
       </c>
       <c r="R12" t="n">
-        <v>7266141</v>
+        <v>7266152</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819467</v>
+        <v>119819444</v>
       </c>
       <c r="B13" t="n">
-        <v>90562</v>
+        <v>91850</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,21 +1902,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618344</v>
+        <v>618376</v>
       </c>
       <c r="R13" t="n">
-        <v>7266305</v>
+        <v>7265700</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819466</v>
+        <v>119819449</v>
       </c>
       <c r="B14" t="n">
-        <v>92030</v>
+        <v>91902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618486</v>
+        <v>618608</v>
       </c>
       <c r="R14" t="n">
-        <v>7266232</v>
+        <v>7265761</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819461</v>
+        <v>119819467</v>
       </c>
       <c r="B15" t="n">
-        <v>91844</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4365</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618495</v>
+        <v>618344</v>
       </c>
       <c r="R15" t="n">
-        <v>7266270</v>
+        <v>7266305</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819456</v>
+        <v>119819447</v>
       </c>
       <c r="B16" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618574</v>
+        <v>618412</v>
       </c>
       <c r="R16" t="n">
-        <v>7266106</v>
+        <v>7265705</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819439</v>
+        <v>119819464</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618264</v>
+        <v>618485</v>
       </c>
       <c r="R17" t="n">
-        <v>7265719</v>
+        <v>7266243</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819450</v>
+        <v>119819436</v>
       </c>
       <c r="B18" t="n">
-        <v>91834</v>
+        <v>90825</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,25 +2453,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4362</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618632</v>
+        <v>618304</v>
       </c>
       <c r="R18" t="n">
-        <v>7265743</v>
+        <v>7265775</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819468</v>
+        <v>119819456</v>
       </c>
       <c r="B19" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618354</v>
+        <v>618574</v>
       </c>
       <c r="R19" t="n">
-        <v>7266194</v>
+        <v>7266106</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819446</v>
+        <v>119819466</v>
       </c>
       <c r="B20" t="n">
-        <v>91852</v>
+        <v>92048</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,25 +2675,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>2079</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618407</v>
+        <v>618486</v>
       </c>
       <c r="R20" t="n">
-        <v>7265700</v>
+        <v>7266232</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819438</v>
+        <v>119819468</v>
       </c>
       <c r="B21" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,30 +2786,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618317</v>
+        <v>618354</v>
       </c>
       <c r="R21" t="n">
-        <v>7265937</v>
+        <v>7266194</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819447</v>
+        <v>119819443</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618412</v>
+        <v>618376</v>
       </c>
       <c r="R22" t="n">
-        <v>7265705</v>
+        <v>7265703</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819455</v>
+        <v>119819460</v>
       </c>
       <c r="B23" t="n">
-        <v>91832</v>
+        <v>89229</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>1593</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618552</v>
+        <v>618478</v>
       </c>
       <c r="R23" t="n">
-        <v>7266102</v>
+        <v>7266264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819443</v>
+        <v>119819438</v>
       </c>
       <c r="B24" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618376</v>
+        <v>618317</v>
       </c>
       <c r="R24" t="n">
-        <v>7265703</v>
+        <v>7265937</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819458</v>
+        <v>119819448</v>
       </c>
       <c r="B25" t="n">
-        <v>91832</v>
+        <v>91874</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3234,21 +3234,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618571</v>
+        <v>618486</v>
       </c>
       <c r="R25" t="n">
-        <v>7266173</v>
+        <v>7265809</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819464</v>
+        <v>119819451</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3373,13 +3373,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618485</v>
+        <v>618639</v>
       </c>
       <c r="R26" t="n">
-        <v>7266243</v>
+        <v>7265727</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819441</v>
+        <v>119819461</v>
       </c>
       <c r="B27" t="n">
-        <v>91832</v>
+        <v>91862</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,13 +3484,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618302</v>
+        <v>618495</v>
       </c>
       <c r="R27" t="n">
-        <v>7265772</v>
+        <v>7266270</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819436</v>
+        <v>119819435</v>
       </c>
       <c r="B28" t="n">
-        <v>90807</v>
+        <v>91844</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3563,25 +3563,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>65</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618304</v>
+        <v>618300</v>
       </c>
       <c r="R28" t="n">
-        <v>7265775</v>
+        <v>7265774</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819448</v>
+        <v>119819459</v>
       </c>
       <c r="B29" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,26 +3678,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618486</v>
+        <v>618572</v>
       </c>
       <c r="R29" t="n">
-        <v>7265809</v>
+        <v>7266176</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819460</v>
+        <v>119819465</v>
       </c>
       <c r="B30" t="n">
-        <v>89212</v>
+        <v>91852</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3785,30 +3785,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1593</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618478</v>
+        <v>618489</v>
       </c>
       <c r="R30" t="n">
-        <v>7266264</v>
+        <v>7266234</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819465</v>
+        <v>119819457</v>
       </c>
       <c r="B31" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618489</v>
+        <v>618642</v>
       </c>
       <c r="R31" t="n">
-        <v>7266234</v>
+        <v>7266121</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819437</v>
+        <v>119819453</v>
       </c>
       <c r="B32" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618321</v>
+        <v>618499</v>
       </c>
       <c r="R32" t="n">
-        <v>7265970</v>
+        <v>7266141</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819459</v>
+        <v>119819440</v>
       </c>
       <c r="B33" t="n">
-        <v>91834</v>
+        <v>91862</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4118,30 +4118,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618572</v>
+        <v>618304</v>
       </c>
       <c r="R33" t="n">
-        <v>7266176</v>
+        <v>7265777</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819451</v>
+        <v>119819441</v>
       </c>
       <c r="B34" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4229,25 +4229,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618639</v>
+        <v>618302</v>
       </c>
       <c r="R34" t="n">
-        <v>7265727</v>
+        <v>7265772</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819452</v>
+        <v>119819458</v>
       </c>
       <c r="B35" t="n">
-        <v>91840</v>
+        <v>91850</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4340,25 +4340,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618670</v>
+        <v>618571</v>
       </c>
       <c r="R35" t="n">
-        <v>7265829</v>
+        <v>7266173</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819449</v>
+        <v>119819446</v>
       </c>
       <c r="B36" t="n">
-        <v>91884</v>
+        <v>91870</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4451,25 +4451,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4483,10 +4483,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618608</v>
+        <v>618407</v>
       </c>
       <c r="R36" t="n">
-        <v>7265761</v>
+        <v>7265700</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819444</v>
+        <v>119819442</v>
       </c>
       <c r="B37" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618376</v>
+        <v>618304</v>
       </c>
       <c r="R37" t="n">
-        <v>7265700</v>
+        <v>7265777</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819442</v>
+        <v>119819439</v>
       </c>
       <c r="B38" t="n">
-        <v>91834</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,25 +4673,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618304</v>
+        <v>618264</v>
       </c>
       <c r="R38" t="n">
-        <v>7265777</v>
+        <v>7265719</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819454</v>
+        <v>119819437</v>
       </c>
       <c r="B39" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4784,30 +4784,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4816,13 +4816,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618497</v>
+        <v>618321</v>
       </c>
       <c r="R39" t="n">
-        <v>7266152</v>
+        <v>7265970</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819440</v>
+        <v>119819450</v>
       </c>
       <c r="B40" t="n">
-        <v>91844</v>
+        <v>91852</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4895,25 +4895,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618304</v>
+        <v>618632</v>
       </c>
       <c r="R40" t="n">
-        <v>7265777</v>
+        <v>7265743</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819460</v>
+        <v>119819438</v>
       </c>
       <c r="B23" t="n">
-        <v>89229</v>
+        <v>91902</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1593</v>
+        <v>5449</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618478</v>
+        <v>618317</v>
       </c>
       <c r="R23" t="n">
-        <v>7266264</v>
+        <v>7265937</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819438</v>
+        <v>119819460</v>
       </c>
       <c r="B24" t="n">
-        <v>91902</v>
+        <v>89229</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,30 +3119,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5449</v>
+        <v>1593</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618317</v>
+        <v>618478</v>
       </c>
       <c r="R24" t="n">
-        <v>7265937</v>
+        <v>7266264</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819463</v>
+        <v>119819465</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,26 +1569,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618487</v>
+        <v>618489</v>
       </c>
       <c r="R10" t="n">
-        <v>7266259</v>
+        <v>7266234</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819455</v>
+        <v>119819461</v>
       </c>
       <c r="B11" t="n">
-        <v>91850</v>
+        <v>91862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,25 +1676,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>4365</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618552</v>
+        <v>618495</v>
       </c>
       <c r="R11" t="n">
-        <v>7266102</v>
+        <v>7266270</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819454</v>
+        <v>119819450</v>
       </c>
       <c r="B12" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1787,30 +1787,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1819,13 +1819,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618497</v>
+        <v>618632</v>
       </c>
       <c r="R12" t="n">
-        <v>7266152</v>
+        <v>7265743</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819444</v>
+        <v>119819441</v>
       </c>
       <c r="B13" t="n">
         <v>91850</v>
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618376</v>
+        <v>618302</v>
       </c>
       <c r="R13" t="n">
-        <v>7265700</v>
+        <v>7265772</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819449</v>
+        <v>119819466</v>
       </c>
       <c r="B14" t="n">
-        <v>91902</v>
+        <v>92048</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>2079</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618608</v>
+        <v>618486</v>
       </c>
       <c r="R14" t="n">
-        <v>7265761</v>
+        <v>7266232</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819467</v>
+        <v>119819446</v>
       </c>
       <c r="B15" t="n">
-        <v>90580</v>
+        <v>91870</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618344</v>
+        <v>618407</v>
       </c>
       <c r="R15" t="n">
-        <v>7266305</v>
+        <v>7265700</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,10 +2219,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819447</v>
+        <v>119819458</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2231,30 +2231,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618412</v>
+        <v>618571</v>
       </c>
       <c r="R16" t="n">
-        <v>7265705</v>
+        <v>7266173</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819464</v>
+        <v>119819442</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,30 +2342,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2374,13 +2374,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>618485</v>
+        <v>618304</v>
       </c>
       <c r="R17" t="n">
-        <v>7266243</v>
+        <v>7265777</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819436</v>
+        <v>119819447</v>
       </c>
       <c r="B18" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,30 +2453,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618304</v>
+        <v>618412</v>
       </c>
       <c r="R18" t="n">
-        <v>7265775</v>
+        <v>7265705</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,7 +2552,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819456</v>
+        <v>119819451</v>
       </c>
       <c r="B19" t="n">
         <v>91858</v>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618574</v>
+        <v>618639</v>
       </c>
       <c r="R19" t="n">
-        <v>7266106</v>
+        <v>7265727</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819466</v>
+        <v>119819454</v>
       </c>
       <c r="B20" t="n">
-        <v>92048</v>
+        <v>91858</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618486</v>
+        <v>618497</v>
       </c>
       <c r="R20" t="n">
-        <v>7266232</v>
+        <v>7266152</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819468</v>
+        <v>119819455</v>
       </c>
       <c r="B21" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2786,30 +2786,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618354</v>
+        <v>618552</v>
       </c>
       <c r="R21" t="n">
-        <v>7266194</v>
+        <v>7266102</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819443</v>
+        <v>119819468</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618376</v>
+        <v>618354</v>
       </c>
       <c r="R22" t="n">
-        <v>7265703</v>
+        <v>7266194</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819438</v>
+        <v>119819456</v>
       </c>
       <c r="B23" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618317</v>
+        <v>618574</v>
       </c>
       <c r="R23" t="n">
-        <v>7265937</v>
+        <v>7266106</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819460</v>
+        <v>119819436</v>
       </c>
       <c r="B24" t="n">
-        <v>89229</v>
+        <v>90825</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3123,26 +3123,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1593</v>
+        <v>65</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618478</v>
+        <v>618304</v>
       </c>
       <c r="R24" t="n">
-        <v>7266264</v>
+        <v>7265775</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819448</v>
+        <v>119819460</v>
       </c>
       <c r="B25" t="n">
-        <v>91874</v>
+        <v>89229</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,30 +3230,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
+        <v>1593</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618486</v>
+        <v>618478</v>
       </c>
       <c r="R25" t="n">
-        <v>7265809</v>
+        <v>7266264</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819451</v>
+        <v>119819467</v>
       </c>
       <c r="B26" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3341,25 +3341,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618639</v>
+        <v>618344</v>
       </c>
       <c r="R26" t="n">
-        <v>7265727</v>
+        <v>7266305</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819461</v>
+        <v>119819449</v>
       </c>
       <c r="B27" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618495</v>
+        <v>618608</v>
       </c>
       <c r="R27" t="n">
-        <v>7266270</v>
+        <v>7265761</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819435</v>
+        <v>119819438</v>
       </c>
       <c r="B28" t="n">
-        <v>91844</v>
+        <v>91902</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618300</v>
+        <v>618317</v>
       </c>
       <c r="R28" t="n">
-        <v>7265774</v>
+        <v>7265937</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819465</v>
+        <v>119819463</v>
       </c>
       <c r="B30" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3789,26 +3789,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618489</v>
+        <v>618487</v>
       </c>
       <c r="R30" t="n">
-        <v>7266234</v>
+        <v>7266259</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819457</v>
+        <v>119819440</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3896,30 +3896,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>618642</v>
+        <v>618304</v>
       </c>
       <c r="R31" t="n">
-        <v>7266121</v>
+        <v>7265777</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819453</v>
+        <v>119819443</v>
       </c>
       <c r="B32" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4011,21 +4011,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4039,10 +4039,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618499</v>
+        <v>618376</v>
       </c>
       <c r="R32" t="n">
-        <v>7266141</v>
+        <v>7265703</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4106,10 +4106,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819440</v>
+        <v>119819439</v>
       </c>
       <c r="B33" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4118,25 +4118,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618304</v>
+        <v>618264</v>
       </c>
       <c r="R33" t="n">
-        <v>7265777</v>
+        <v>7265719</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819441</v>
+        <v>119819453</v>
       </c>
       <c r="B34" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4233,21 +4233,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618302</v>
+        <v>618499</v>
       </c>
       <c r="R34" t="n">
-        <v>7265772</v>
+        <v>7266141</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819458</v>
+        <v>119819444</v>
       </c>
       <c r="B35" t="n">
         <v>91850</v>
@@ -4372,13 +4372,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618571</v>
+        <v>618376</v>
       </c>
       <c r="R35" t="n">
-        <v>7266173</v>
+        <v>7265700</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819446</v>
+        <v>119819464</v>
       </c>
       <c r="B36" t="n">
-        <v>91870</v>
+        <v>91858</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4455,26 +4455,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4483,13 +4483,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618407</v>
+        <v>618485</v>
       </c>
       <c r="R36" t="n">
-        <v>7265700</v>
+        <v>7266243</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819442</v>
+        <v>119819435</v>
       </c>
       <c r="B37" t="n">
-        <v>91852</v>
+        <v>91844</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4566,21 +4566,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618304</v>
+        <v>618300</v>
       </c>
       <c r="R37" t="n">
-        <v>7265777</v>
+        <v>7265774</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819439</v>
+        <v>119819448</v>
       </c>
       <c r="B38" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4673,25 +4673,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618264</v>
+        <v>618486</v>
       </c>
       <c r="R38" t="n">
-        <v>7265719</v>
+        <v>7265809</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819450</v>
+        <v>119819457</v>
       </c>
       <c r="B40" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4895,30 +4895,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4927,10 +4927,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618632</v>
+        <v>618642</v>
       </c>
       <c r="R40" t="n">
-        <v>7265743</v>
+        <v>7266121</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819452</v>
+        <v>119819465</v>
       </c>
       <c r="B9" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618670</v>
+        <v>618489</v>
       </c>
       <c r="R9" t="n">
-        <v>7265829</v>
+        <v>7266234</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819465</v>
+        <v>119819461</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,25 +1565,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618489</v>
+        <v>618495</v>
       </c>
       <c r="R10" t="n">
-        <v>7266234</v>
+        <v>7266270</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819461</v>
+        <v>119819452</v>
       </c>
       <c r="B11" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1676,25 +1676,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1708,10 +1708,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618495</v>
+        <v>618670</v>
       </c>
       <c r="R11" t="n">
-        <v>7266270</v>
+        <v>7265829</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819456</v>
+        <v>119819436</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>90825</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,30 +3008,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3040,13 +3040,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618574</v>
+        <v>618304</v>
       </c>
       <c r="R23" t="n">
-        <v>7266106</v>
+        <v>7265775</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819436</v>
+        <v>119819460</v>
       </c>
       <c r="B24" t="n">
-        <v>90825</v>
+        <v>89229</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3123,26 +3123,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>65</v>
+        <v>1593</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618304</v>
+        <v>618478</v>
       </c>
       <c r="R24" t="n">
-        <v>7265775</v>
+        <v>7266264</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819460</v>
+        <v>119819456</v>
       </c>
       <c r="B25" t="n">
-        <v>89229</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,30 +3230,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1593</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618478</v>
+        <v>618574</v>
       </c>
       <c r="R25" t="n">
-        <v>7266264</v>
+        <v>7266106</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119819465</v>
+        <v>119819443</v>
       </c>
       <c r="B9" t="n">
-        <v>91852</v>
+        <v>91902</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>618489</v>
+        <v>618376</v>
       </c>
       <c r="R9" t="n">
-        <v>7266234</v>
+        <v>7265703</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119819461</v>
+        <v>119819457</v>
       </c>
       <c r="B10" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,30 +1565,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1597,10 +1597,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>618495</v>
+        <v>618642</v>
       </c>
       <c r="R10" t="n">
-        <v>7266270</v>
+        <v>7266121</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119819452</v>
+        <v>119819464</v>
       </c>
       <c r="B11" t="n">
         <v>91858</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1708,13 +1708,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>618670</v>
+        <v>618485</v>
       </c>
       <c r="R11" t="n">
-        <v>7265829</v>
+        <v>7266243</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119819450</v>
+        <v>119819442</v>
       </c>
       <c r="B12" t="n">
         <v>91852</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>618632</v>
+        <v>618304</v>
       </c>
       <c r="R12" t="n">
-        <v>7265743</v>
+        <v>7265777</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1886,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119819441</v>
+        <v>119819459</v>
       </c>
       <c r="B13" t="n">
-        <v>91850</v>
+        <v>91852</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1902,26 +1902,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1930,13 +1930,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>618302</v>
+        <v>618572</v>
       </c>
       <c r="R13" t="n">
-        <v>7265772</v>
+        <v>7266176</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119819466</v>
+        <v>119819444</v>
       </c>
       <c r="B14" t="n">
-        <v>92048</v>
+        <v>91850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2013,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2079</v>
+        <v>4361</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>618486</v>
+        <v>618376</v>
       </c>
       <c r="R14" t="n">
-        <v>7266232</v>
+        <v>7265700</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119819446</v>
+        <v>119819435</v>
       </c>
       <c r="B15" t="n">
-        <v>91870</v>
+        <v>91844</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>3100</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2152,10 +2152,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>618407</v>
+        <v>618300</v>
       </c>
       <c r="R15" t="n">
-        <v>7265700</v>
+        <v>7265774</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119819458</v>
+        <v>119819455</v>
       </c>
       <c r="B16" t="n">
         <v>91850</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>618571</v>
+        <v>618552</v>
       </c>
       <c r="R16" t="n">
-        <v>7266173</v>
+        <v>7266102</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,10 +2330,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119819442</v>
+        <v>119819440</v>
       </c>
       <c r="B17" t="n">
-        <v>91852</v>
+        <v>91862</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2342,25 +2342,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>4365</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2441,10 +2441,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119819447</v>
+        <v>119819461</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2453,30 +2453,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>618412</v>
+        <v>618495</v>
       </c>
       <c r="R18" t="n">
-        <v>7265705</v>
+        <v>7266270</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2552,10 +2552,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119819451</v>
+        <v>119819467</v>
       </c>
       <c r="B19" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2564,25 +2564,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>618639</v>
+        <v>618344</v>
       </c>
       <c r="R19" t="n">
-        <v>7265727</v>
+        <v>7266305</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2663,10 +2663,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119819454</v>
+        <v>119819458</v>
       </c>
       <c r="B20" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>618497</v>
+        <v>618571</v>
       </c>
       <c r="R20" t="n">
-        <v>7266152</v>
+        <v>7266173</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2774,10 +2774,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119819455</v>
+        <v>119819449</v>
       </c>
       <c r="B21" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2790,21 +2790,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>618552</v>
+        <v>618608</v>
       </c>
       <c r="R21" t="n">
-        <v>7266102</v>
+        <v>7265761</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119819468</v>
+        <v>119819438</v>
       </c>
       <c r="B22" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2897,30 +2897,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2929,10 +2929,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>618354</v>
+        <v>618317</v>
       </c>
       <c r="R22" t="n">
-        <v>7266194</v>
+        <v>7265937</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119819436</v>
+        <v>119819451</v>
       </c>
       <c r="B23" t="n">
-        <v>90825</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3008,25 +3008,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3040,10 +3040,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>618304</v>
+        <v>618639</v>
       </c>
       <c r="R23" t="n">
-        <v>7265775</v>
+        <v>7265727</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3107,10 +3107,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119819460</v>
+        <v>119819446</v>
       </c>
       <c r="B24" t="n">
-        <v>89229</v>
+        <v>91870</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3119,30 +3119,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1593</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3151,13 +3151,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>618478</v>
+        <v>618407</v>
       </c>
       <c r="R24" t="n">
-        <v>7266264</v>
+        <v>7265700</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119819456</v>
+        <v>119819453</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3230,30 +3230,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3262,13 +3262,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>618574</v>
+        <v>618499</v>
       </c>
       <c r="R25" t="n">
-        <v>7266106</v>
+        <v>7266141</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119819467</v>
+        <v>119819466</v>
       </c>
       <c r="B26" t="n">
-        <v>90580</v>
+        <v>92048</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>2079</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>618344</v>
+        <v>618486</v>
       </c>
       <c r="R26" t="n">
-        <v>7266305</v>
+        <v>7266232</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3440,10 +3440,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119819449</v>
+        <v>119819448</v>
       </c>
       <c r="B27" t="n">
-        <v>91902</v>
+        <v>91874</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3456,21 +3456,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5449</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>618608</v>
+        <v>618486</v>
       </c>
       <c r="R27" t="n">
-        <v>7265761</v>
+        <v>7265809</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3551,10 +3551,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119819438</v>
+        <v>119819437</v>
       </c>
       <c r="B28" t="n">
-        <v>91902</v>
+        <v>91852</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3567,21 +3567,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>618317</v>
+        <v>618321</v>
       </c>
       <c r="R28" t="n">
-        <v>7265937</v>
+        <v>7265970</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3662,10 +3662,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119819459</v>
+        <v>119819463</v>
       </c>
       <c r="B29" t="n">
-        <v>91852</v>
+        <v>91850</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3678,26 +3678,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>618572</v>
+        <v>618487</v>
       </c>
       <c r="R29" t="n">
-        <v>7266176</v>
+        <v>7266259</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119819463</v>
+        <v>119819441</v>
       </c>
       <c r="B30" t="n">
         <v>91850</v>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3817,13 +3817,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>618487</v>
+        <v>618302</v>
       </c>
       <c r="R30" t="n">
-        <v>7266259</v>
+        <v>7265772</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119819440</v>
+        <v>119819436</v>
       </c>
       <c r="B31" t="n">
-        <v>91862</v>
+        <v>90825</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3900,21 +3900,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3931,7 +3931,7 @@
         <v>618304</v>
       </c>
       <c r="R31" t="n">
-        <v>7265777</v>
+        <v>7265775</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3995,10 +3995,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119819443</v>
+        <v>119819456</v>
       </c>
       <c r="B32" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4007,30 +4007,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4039,13 +4039,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>618376</v>
+        <v>618574</v>
       </c>
       <c r="R32" t="n">
-        <v>7265703</v>
+        <v>7266106</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119819439</v>
+        <v>119819452</v>
       </c>
       <c r="B33" t="n">
         <v>91858</v>
@@ -4150,10 +4150,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>618264</v>
+        <v>618670</v>
       </c>
       <c r="R33" t="n">
-        <v>7265719</v>
+        <v>7265829</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4217,10 +4217,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119819453</v>
+        <v>119819454</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4229,30 +4229,30 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>618499</v>
+        <v>618497</v>
       </c>
       <c r="R34" t="n">
-        <v>7266141</v>
+        <v>7266152</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4328,10 +4328,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119819444</v>
+        <v>119819468</v>
       </c>
       <c r="B35" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4340,30 +4340,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>618376</v>
+        <v>618354</v>
       </c>
       <c r="R35" t="n">
-        <v>7265700</v>
+        <v>7266194</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4439,10 +4439,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119819464</v>
+        <v>119819465</v>
       </c>
       <c r="B36" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4451,30 +4451,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4483,13 +4483,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>618485</v>
+        <v>618489</v>
       </c>
       <c r="R36" t="n">
-        <v>7266243</v>
+        <v>7266234</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4550,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119819435</v>
+        <v>119819447</v>
       </c>
       <c r="B37" t="n">
-        <v>91844</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4562,30 +4562,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4594,10 +4594,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>618300</v>
+        <v>618412</v>
       </c>
       <c r="R37" t="n">
-        <v>7265774</v>
+        <v>7265705</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4661,10 +4661,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119819448</v>
+        <v>119819450</v>
       </c>
       <c r="B38" t="n">
-        <v>91874</v>
+        <v>91852</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4677,21 +4677,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4705,10 +4705,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>618486</v>
+        <v>618632</v>
       </c>
       <c r="R38" t="n">
-        <v>7265809</v>
+        <v>7265743</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4772,10 +4772,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119819437</v>
+        <v>119819439</v>
       </c>
       <c r="B39" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4784,25 +4784,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4816,10 +4816,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>618321</v>
+        <v>618264</v>
       </c>
       <c r="R39" t="n">
-        <v>7265970</v>
+        <v>7265719</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119819457</v>
+        <v>119819460</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>89229</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4895,30 +4895,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>1593</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4927,13 +4927,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>618642</v>
+        <v>618478</v>
       </c>
       <c r="R40" t="n">
-        <v>7266121</v>
+        <v>7266264</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -4997,7 +4997,7 @@
         <v>121152534</v>
       </c>
       <c r="B41" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -4997,7 +4997,7 @@
         <v>121152534</v>
       </c>
       <c r="B41" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -4997,7 +4997,7 @@
         <v>121152534</v>
       </c>
       <c r="B41" t="n">
-        <v>91985</v>
+        <v>91986</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -4997,7 +4997,7 @@
         <v>121152534</v>
       </c>
       <c r="B41" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AY42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5103,6 +5103,112 @@
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126379869</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78735</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sorsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>618614</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7265764</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39230-2020 artfynd.xlsx
+++ b/artfynd/A 39230-2020 artfynd.xlsx
@@ -5108,7 +5108,7 @@
         <v>126379869</v>
       </c>
       <c r="B42" t="n">
-        <v>78735</v>
+        <v>78738</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
